--- a/diseases/d011/2000-2004.xlsx
+++ b/diseases/d011/2000-2004.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>0</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2693,9 +2684,6 @@
       <c r="O13" t="n">
         <v>1</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -3385,9 +3373,6 @@
       <c r="O17" t="n">
         <v>0</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0</v>
       </c>
@@ -4077,9 +4062,6 @@
       <c r="O21" t="n">
         <v>0</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0</v>
       </c>
@@ -4769,9 +4751,6 @@
       <c r="O25" t="n">
         <v>1</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.01931918608655401</v>
       </c>
@@ -5461,9 +5440,6 @@
       <c r="O29" t="n">
         <v>0</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0</v>
       </c>
@@ -6153,9 +6129,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6845,9 +6818,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7537,9 +7507,6 @@
       <c r="O41" t="n">
         <v>0</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0</v>
       </c>
@@ -8229,9 +8196,6 @@
       <c r="O45" t="n">
         <v>0</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0</v>
       </c>
@@ -8921,9 +8885,6 @@
       <c r="O49" t="n">
         <v>0</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0</v>
       </c>
@@ -9613,9 +9574,6 @@
       <c r="O53" t="n">
         <v>0</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0</v>
       </c>
@@ -10157,9 +10115,6 @@
       <c r="O56" t="n">
         <v>0</v>
       </c>
-      <c r="Q56" t="n">
-        <v>0</v>
-      </c>
       <c r="R56" t="n">
         <v>0</v>
       </c>
@@ -10701,9 +10656,6 @@
       <c r="O59" t="n">
         <v>1</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -11393,9 +11345,6 @@
       <c r="O63" t="n">
         <v>0</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0</v>
       </c>
@@ -12085,9 +12034,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -12777,9 +12723,6 @@
       <c r="O71" t="n">
         <v>1</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -13469,9 +13412,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -14161,9 +14101,6 @@
       <c r="O79" t="n">
         <v>1</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -14853,9 +14790,6 @@
       <c r="O83" t="n">
         <v>0</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0</v>
       </c>
@@ -15545,9 +15479,6 @@
       <c r="O87" t="n">
         <v>1</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.01927535832409241</v>
       </c>
@@ -16237,9 +16168,6 @@
       <c r="O91" t="n">
         <v>0</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0</v>
       </c>
@@ -16929,9 +16857,6 @@
       <c r="O95" t="n">
         <v>0</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0</v>
       </c>
@@ -17621,9 +17546,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18313,9 +18235,6 @@
       <c r="O103" t="n">
         <v>1</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -18857,9 +18776,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -19401,9 +19317,6 @@
       <c r="O109" t="n">
         <v>0</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>0</v>
       </c>
@@ -20093,9 +20006,6 @@
       <c r="O113" t="n">
         <v>0</v>
       </c>
-      <c r="Q113" t="n">
-        <v>0</v>
-      </c>
       <c r="R113" t="n">
         <v>0</v>
       </c>
@@ -20785,9 +20695,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -21477,9 +21384,6 @@
       <c r="O121" t="n">
         <v>1</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -22169,9 +22073,6 @@
       <c r="O125" t="n">
         <v>0</v>
       </c>
-      <c r="Q125" t="n">
-        <v>0</v>
-      </c>
       <c r="R125" t="n">
         <v>0</v>
       </c>
@@ -22861,9 +22762,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -23553,9 +23451,6 @@
       <c r="O133" t="n">
         <v>0</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0</v>
       </c>
@@ -24245,9 +24140,6 @@
       <c r="O137" t="n">
         <v>0</v>
       </c>
-      <c r="Q137" t="n">
-        <v>0</v>
-      </c>
       <c r="R137" t="n">
         <v>0</v>
       </c>
@@ -24937,9 +24829,6 @@
       <c r="O141" t="n">
         <v>1</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0.01922875021199697</v>
       </c>
@@ -25629,9 +25518,6 @@
       <c r="O145" t="n">
         <v>0</v>
       </c>
-      <c r="Q145" t="n">
-        <v>0</v>
-      </c>
       <c r="R145" t="n">
         <v>0</v>
       </c>
@@ -26321,9 +26207,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -27013,9 +26896,6 @@
       <c r="O153" t="n">
         <v>0</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0</v>
       </c>
@@ -27557,9 +27437,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -28101,9 +27978,6 @@
       <c r="O159" t="n">
         <v>0</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0</v>
       </c>
@@ -28941,9 +28815,6 @@
       <c r="O164" t="n">
         <v>0</v>
       </c>
-      <c r="Q164" t="n">
-        <v>0</v>
-      </c>
       <c r="R164" t="n">
         <v>0</v>
       </c>
@@ -29781,9 +29652,6 @@
       <c r="O169" t="n">
         <v>0</v>
       </c>
-      <c r="Q169" t="n">
-        <v>0</v>
-      </c>
       <c r="R169" t="n">
         <v>0</v>
       </c>
@@ -30621,9 +30489,6 @@
       <c r="O174" t="n">
         <v>1</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -31461,9 +31326,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -32153,9 +32015,6 @@
       <c r="O183" t="n">
         <v>0</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>0</v>
       </c>
@@ -32845,9 +32704,6 @@
       <c r="O187" t="n">
         <v>0</v>
       </c>
-      <c r="Q187" t="n">
-        <v>0</v>
-      </c>
       <c r="R187" t="n">
         <v>0</v>
       </c>
@@ -33537,9 +33393,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -34377,9 +34230,6 @@
       <c r="O196" t="n">
         <v>0</v>
       </c>
-      <c r="Q196" t="n">
-        <v>0</v>
-      </c>
       <c r="R196" t="n">
         <v>0</v>
       </c>
@@ -35217,9 +35067,6 @@
       <c r="O201" t="n">
         <v>0</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0</v>
       </c>
@@ -36057,9 +35904,6 @@
       <c r="O206" t="n">
         <v>1</v>
       </c>
-      <c r="Q206" t="n">
-        <v>0</v>
-      </c>
       <c r="R206" t="n">
         <v>0.01918297779282576</v>
       </c>
@@ -36749,9 +36593,6 @@
       <c r="O210" t="n">
         <v>0</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0</v>
       </c>
@@ -37293,9 +37134,6 @@
       <c r="O213" t="n">
         <v>0</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0</v>
       </c>
@@ -37985,9 +37823,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -38677,9 +38512,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -39517,9 +39349,6 @@
       <c r="O226" t="n">
         <v>0</v>
       </c>
-      <c r="Q226" t="n">
-        <v>0</v>
-      </c>
       <c r="R226" t="n">
         <v>0</v>
       </c>
@@ -40357,9 +40186,6 @@
       <c r="O231" t="n">
         <v>0</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0</v>
       </c>
@@ -41197,9 +41023,6 @@
       <c r="O236" t="n">
         <v>2</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.0382544641046887</v>
       </c>
@@ -42037,9 +41860,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -42877,9 +42697,6 @@
       <c r="O246" t="n">
         <v>0</v>
       </c>
-      <c r="Q246" t="n">
-        <v>0</v>
-      </c>
       <c r="R246" t="n">
         <v>0</v>
       </c>
@@ -43717,9 +43534,6 @@
       <c r="O251" t="n">
         <v>0</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0</v>
       </c>
@@ -44409,9 +44223,6 @@
       <c r="O255" t="n">
         <v>0</v>
       </c>
-      <c r="Q255" t="n">
-        <v>0</v>
-      </c>
       <c r="R255" t="n">
         <v>0</v>
       </c>
@@ -45101,9 +44912,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -45939,9 +45747,6 @@
         <v>0</v>
       </c>
       <c r="O264" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q264" t="n">
         <v>0</v>
       </c>
       <c r="R264" t="n">
